--- a/workflows/anomaly-alert-flow/out/预警推送单.xlsx
+++ b/workflows/anomaly-alert-flow/out/预警推送单.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -513,305 +513,721 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>营收连续趋势</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>R3 连续趋势</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>连续 4 天下滑</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-05 → 2026-09-09 累计 -23.1%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>企业微信群机器人、短信值班手机</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>转化率连续趋势</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>R3 连续趋势</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>连续 4 天下滑</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-08 → 2026-09-12 累计 -30.7%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>企业微信群机器人、短信值班手机</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7.90%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>退款 965 元 / 营收 12221 元</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>企业微信群机器人、短信值班手机</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7.90%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>退款 705 元 / 营收 8925 元</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>企业微信群机器人、短信值班手机</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7.90%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>退款 705 元 / 营收 8928 元</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>企业微信群机器人、短信值班手机</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7.89%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>退款 760 元 / 营收 9632 元</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>企业微信群机器人、短信值班手机</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7.89%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>退款 720 元 / 营收 9121 元</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>企业微信群机器人、短信值班手机</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>🔴 高</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-80.2%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>营收 2389 元（前一日 12063 元）</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>企业微信群机器人、短信值班手机</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>营收环比</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>营收同比</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>R4 季节性（同比优先）</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-25.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>去年同期 11922 元，本期 8942 元</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>企业微信群机器人</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>R1 绝对阈值</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-30.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>营收 6247 元（前一日 8929 元）</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>企业微信群机器人、短信值班手机</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>访客 9364，订单 136</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>企业微信群机器人</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>转化率离群</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Z=-2.01（μ=2.7，σ=0.6）</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>企业微信群机器人</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>🟡 中</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>访客 10090，订单 148</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>企业微信群机器人</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>访客 9733，订单 143</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>企业微信群机器人</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>营收离群</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>R2 离群（Z-score(2σ)）</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>6247元</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Z=-2.30（μ=9521.8，σ=1423.8）</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2389元</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Z=-3.20（μ=9410.8，σ=2194.3）</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>企业微信群机器人</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>🟡 中</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>周三</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>退款率</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>R1 绝对阈值</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>6.79%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>退款 624 元 / 营收 9184 元</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>企业微信群机器人</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>🟡 中</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>周三</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>退款率离群</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>R2 离群（Z-score(2σ)）</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6.79%</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Z=+3.62（μ=2.7，σ=1.1）</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>企业微信群机器人</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>🟡 中</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>周一</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>营收环比</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>R1 绝对阈值</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-22.2%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>营收 9352 元（前一日 12018 元）</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>企业微信群机器人</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>🟡 中</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>周三</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>退款率连续趋势</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>R3 连续趋势</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>连续 4 天下滑</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-09-11 → 2026-09-16 累计 -11.6%</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>企业微信群机器人</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -828,18 +1244,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
@@ -910,62 +1326,620 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-20.6%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>营收 6895 元（前一日 8679 元）</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-34.2%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-38.9%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>同指标 12 小时去重窗口内已推送过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>周一</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>营收环比</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>R1 绝对阈值</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-23.2%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-21.1%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>环比 ≤ -20%</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>营收 8929 元（前一日 11621 元）</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>营收 8986 元（前一日 11396 元）</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>确认异常</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>-2.3%</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>同指标 12 小时去重窗口内已推送过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-25.5%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>营收 11661 元（前一日 15643 元）</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>+11.3%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>+69.1%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>同指标 12 小时去重窗口内已推送过</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-27.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>营收 8925 元（前一日 12221 元）</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-3.0%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>同指标 12 小时去重窗口内已推送过</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>&lt; 1.5%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>访客 1880，订单 15 —— 单日 15 单 &lt; 20 单，失真，只报值不下结论</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>只报值不下结论</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>样本量不足（订单 &lt; 20 单），只报值不推送</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12.72%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>&gt; 5.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>退款 304 元 / 营收 2389 元 —— 订单量不足，失真，只报值不下结论</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>只报值不下结论</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>样本量不足（订单 &lt; 20 单），只报值不推送</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>转化率离群</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Z=-3.05（μ=2.7，σ=0.6） —— 当日仅 15 单，样本不足，只报值不下结论</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>只报值不下结论</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>样本量不足（订单 &lt; 20 单），只报值不推送</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>退款率离群</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12.72%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Z=+3.28（μ=3.7，σ=2.7） —— 当日仅 15 单，样本不足，只报值不下结论</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>只报值不下结论</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>样本量不足（订单 &lt; 20 单），只报值不推送</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>营收离群</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>拦截</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15643元</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Z=+2.84（μ=9410.8，σ=2194.3）</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>特殊期，需人工判断 —— 已拦截（促销日）</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>+55.8%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+80.2%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>特殊期（促销/节假日），仅记录不推送</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>拦截</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-22.3%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>营收 7089 元（前一日 9121 元）</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>特殊期，需人工判断 —— 已拦截（节假日）</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-29.4%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-54.7%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>特殊期（促销/节假日），仅记录不推送</t>
         </is>
       </c>
     </row>
@@ -1130,12 +2104,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1180,6 +2154,28 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>未补零；环比在缺失处断开，不得跨缺口比较，否则会制造假跌</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>单日样本量不足</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-27（15 单）</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>转化率 0.8%、退款率 12.72%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>订单 &lt; 20 单，转化率与退款率失真 —— 只报值不下结论</t>
         </is>
       </c>
     </row>
@@ -1245,7 +2241,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1293,7 +2289,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1305,7 +2301,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1317,7 +2313,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1329,7 +2325,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1341,7 +2337,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1353,7 +2349,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>152349</t>
+          <t>272913</t>
         </is>
       </c>
     </row>
@@ -1365,7 +2361,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.71</t>
         </is>
       </c>
     </row>
@@ -1377,7 +2373,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.46</t>
         </is>
       </c>
     </row>
